--- a/kobo_forms/satisfaction_institution.xlsx
+++ b/kobo_forms/satisfaction_institution.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:K21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,6 +466,11 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
+          <t>calculation</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
           <t>appearance</t>
         </is>
       </c>
@@ -473,157 +478,126 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>select_one_from_file institutions.csv</t>
+          <t>start</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>id_institution</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Institution</t>
-        </is>
-      </c>
+          <t>date_debut</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>select_one_from_file cycles.csv</t>
+          <t>end</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>id_cycle</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Cycle d'enquête</t>
-        </is>
-      </c>
+          <t>date_fin</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>select_one notes</t>
+          <t>today</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>note_formation</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>La formation dans son ensemble</t>
-        </is>
-      </c>
+          <t>date_du_jour</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>select_one notes</t>
+          <t>deviceid</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>note_formateurs</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Les formateurs</t>
-        </is>
-      </c>
+          <t>appareil</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_one notes</t>
+          <t>begin_group</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>note_contenus</t>
+          <t>identification</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Les contenus pédagogiques</t>
+          <t>Identification du répondant</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_one notes</t>
+          <t>select_one_from_file institutions.csv</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>note_equipements</t>
+          <t>institution</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Les équipements et le matériel</t>
+          <t>Institution</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -637,73 +611,76 @@
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_one notes</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>note_accueil</t>
+          <t>fonction</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Les conditions d'accueil</t>
+          <t>Fonction du répondant</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one cycles</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ce_qui_a_bien_fonctionne</t>
+          <t>cycle</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ce qui a le mieux fonctionné</t>
+          <t>Cycle d'enquête</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ce_qu_il_faudrait_ameliorer</t>
+          <t>date_reponse</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ce qu'il faudrait améliorer</t>
+          <t>Date de la réponse</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -711,8 +688,304 @@
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>today()</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>end_group</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>identification</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>begin_group</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Appréciation du dispositif – notes de 1 à 5</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>select_one echelle_5</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>note_qualite_donnees</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>La qualité et la fiabilité des données</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>select_one echelle_5</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>note_outils_collecte</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Les outils de collecte mis à disposition</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>select_one echelle_5</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>note_tableaux_bord</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>L'utilité des tableaux de bord</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>select_one echelle_5</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>note_appui_technique</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>L'appui technique reçu</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>select_one echelle_5</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>note_coordination</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>La coordination entre les structures</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>end_group</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>select_one utilite</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>utilite_dispositif</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Le dispositif de suivi répond-il aux besoins de votre structure ?</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>difficultes</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Difficultés rencontrées dans l'utilisation du dispositif</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>recommandations</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Recommandations d'amélioration</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -725,7 +998,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -748,75 +1021,194 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>notes</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>1</v>
+          <t>cycles</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>cycle_1</t>
+        </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Cycle 1 – novembre 2026</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>notes</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>2</v>
+          <t>cycles</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>cycle_2</t>
+        </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Cycle 2 – mai 2027</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>notes</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>3</v>
+          <t>cycles</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>cycle_3</t>
+        </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Cycle 3 – novembre 2027</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>notes</t>
+          <t>echelle_5</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>notes</t>
+          <t>echelle_5</t>
         </is>
       </c>
       <c r="B6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>echelle_5</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>3</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>echelle_5</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>4</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>echelle_5</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
         <v>5</v>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>utilite</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>pleinement</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Pleinement</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>utilite</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>partiellement</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Partiellement</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>utilite</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>peu</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Peu</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>utilite</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>pas_du_tout</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Pas du tout</t>
         </is>
       </c>
     </row>
@@ -854,7 +1246,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>PDCED Skills - Satisfaction institutionnelle</t>
+          <t>PDCED – Skills | Satisfaction institutionnelle</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
